--- a/data/output/evaluation/openai/internal-consistency/all-criteria/similarity_metrics.xlsx
+++ b/data/output/evaluation/openai/internal-consistency/all-criteria/similarity_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9817369664346797</v>
+        <v>0.9685339620861447</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.7841448532797308</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.7319175454387071</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6317636935053222</v>
+        <v>0.5828202975806771</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -548,17 +548,17 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Komoot</t>
+          <t>Map My Run</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.9685365574221052</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -566,17 +566,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Map My Run</t>
+          <t>MyFitnessPal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9532306376993182</v>
+        <v>0.6591997649528938</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MyFitnessPal</t>
+          <t>Nike Run Club</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8023687558959136</v>
+        <v>0.9633639890708995</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -602,17 +602,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Nike Run Club</t>
+          <t>Pacer Pedometer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9686577684303294</v>
+        <v>0.7466687475068241</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -620,7 +620,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Pacer</t>
+          <t>Pumatrac</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -638,17 +638,17 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Pacer Pedometer &amp; Step Tracker</t>
+          <t>Runkeeper</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.9342327200569945</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -656,17 +656,17 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Polar Flow</t>
+          <t>Runtastic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.9580170197702604</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -674,17 +674,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Pumatrac</t>
+          <t>Samsung Health</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.379642086548638</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -692,17 +692,17 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Runkeeper</t>
+          <t>Sports Tracker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9183996645933803</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -710,7 +710,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Runtastic</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -720,7 +720,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9706602710329612</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -728,17 +728,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Samsung Health</t>
+          <t>Under Armour Record</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4444783184923153</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -746,7 +746,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Sports Tracker</t>
+          <t>Zombies, Run!</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -764,17 +764,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Zwift</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9647638212377321</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -782,77 +782,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Under Armour Record</t>
+          <t>AGGREGATED</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Zombies, Run!</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Zwift</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>AGGREGATED</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.5873015873015873</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.4787012987012987</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.7071428571428571</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.616031746031746</v>
+        <v>0.6589610389610391</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.866904761904762</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7492063492063492</v>
       </c>
     </row>
   </sheetData>
